--- a/tiflow/develop/2.0.0-ballot.1/StructureDefinition-ti-environment.xlsx
+++ b/tiflow/develop/2.0.0-ballot.1/StructureDefinition-ti-environment.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/tiflow-core/StructureDefinition/ti-environment</t>
+    <t>https://gematik.de/fhir/tiflow/StructureDefinition/ti-environment</t>
   </si>
   <si>
     <t>Version</t>
@@ -359,7 +359,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/tiflow-core/ValueSet/ti-environment-vs</t>
+    <t>https://gematik.de/fhir/tiflow/ValueSet/ti-environment-vs</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -705,7 +705,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="49.4609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="45.45703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
